--- a/DB 演習3.xlsx
+++ b/DB 演習3.xlsx
@@ -117,16 +117,16 @@
     <t>演習3-2</t>
   </si>
   <si>
-    <t>支社コード→支社名</t>
-  </si>
-  <si>
-    <t>商品コード→商品名、商品分類コード</t>
-  </si>
-  <si>
-    <t>支店コード→支社名、支店名</t>
-  </si>
-  <si>
-    <t>商品分類コード→分類名</t>
+    <t>部分関数従属・支社コード→支社名</t>
+  </si>
+  <si>
+    <t>部分的関数従属・商品コード→商品名、商品分類コード</t>
+  </si>
+  <si>
+    <t>部分関数従属・支店コード→支社名、支店名</t>
+  </si>
+  <si>
+    <t>部分関数従属・商品分類コード→分類名</t>
   </si>
   <si>
     <t>演習3-3</t>

--- a/DB 演習3.xlsx
+++ b/DB 演習3.xlsx
@@ -117,16 +117,16 @@
     <t>演習3-2</t>
   </si>
   <si>
-    <t>部分関数従属・支社コード→支社名</t>
-  </si>
-  <si>
-    <t>部分的関数従属・商品コード→商品名、商品分類コード</t>
-  </si>
-  <si>
-    <t>部分関数従属・支店コード→支社名、支店名</t>
-  </si>
-  <si>
-    <t>部分関数従属・商品分類コード→分類名</t>
+    <t>部分関係従属・支社コード→支社名</t>
+  </si>
+  <si>
+    <t>部分的関係従属・商品コード→商品名、商品分類コード</t>
+  </si>
+  <si>
+    <t>部分関係従属・支店コード→支社名、支店名</t>
+  </si>
+  <si>
+    <t>部分関係従属・商品分類コード→分類名</t>
   </si>
   <si>
     <t>演習3-3</t>

--- a/DB 演習3.xlsx
+++ b/DB 演習3.xlsx
@@ -117,16 +117,16 @@
     <t>演習3-2</t>
   </si>
   <si>
-    <t>部分関係従属・支社コード→支社名</t>
-  </si>
-  <si>
-    <t>部分的関係従属・商品コード→商品名、商品分類コード</t>
-  </si>
-  <si>
-    <t>部分関係従属・支店コード→支社名、支店名</t>
-  </si>
-  <si>
-    <t>部分関係従属・商品分類コード→分類名</t>
+    <t>部分関数従属・支社コード→支社名</t>
+  </si>
+  <si>
+    <t>部分関数従属・商品コード→商品名、商品分類コード</t>
+  </si>
+  <si>
+    <t>部分関数従属・支店コード→支社名、支店名</t>
+  </si>
+  <si>
+    <t>部分関数従属・商品分類コード→分類名</t>
   </si>
   <si>
     <t>演習3-3</t>

--- a/DB 演習3.xlsx
+++ b/DB 演習3.xlsx
@@ -126,7 +126,7 @@
     <t>部分関数従属・支店コード→支社名、支店名</t>
   </si>
   <si>
-    <t>部分関数従属・商品分類コード→分類名</t>
+    <t>推移的関数従属・商品分類コード→分類名</t>
   </si>
   <si>
     <t>演習3-3</t>

--- a/DB 演習3.xlsx
+++ b/DB 演習3.xlsx
@@ -126,7 +126,7 @@
     <t>部分関数従属・支店コード→支社名、支店名</t>
   </si>
   <si>
-    <t>推移的関数従属・商品分類コード→分類名</t>
+    <t>推移的関数従属・商品コード→商品分類コード→分類名</t>
   </si>
   <si>
     <t>演習3-3</t>
